--- a/diseases/d041/2026-2029.xlsx
+++ b/diseases/d041/2026-2029.xlsx
@@ -29437,6 +29437,151 @@
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>7</v>
+      </c>
+      <c r="O161" t="n">
+        <v>7</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0.005717658852960364</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
+      <c r="AT161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29470,7 +29615,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -29553,7 +29698,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -29563,7 +29708,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -29615,7 +29760,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16704</v>
+        <v>16711</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d041/2026-2029.xlsx
+++ b/diseases/d041/2026-2029.xlsx
@@ -28885,12 +28885,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -28915,7 +28915,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -28924,13 +28924,16 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>5</v>
+        <v>1427</v>
       </c>
       <c r="O157" t="n">
-        <v>5</v>
+        <v>1427</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>0.004084042037828832</v>
+        <v>0.1009969404095159</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -28963,17 +28966,17 @@
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -28983,22 +28986,22 @@
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -29060,7 +29063,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -29069,13 +29072,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O158" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R158" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.004084042037828832</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -29205,7 +29208,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -29214,13 +29217,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O159" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R159" t="n">
-        <v>0.005717658852960364</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -29350,7 +29353,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -29495,7 +29498,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -29577,6 +29580,151 @@
         </is>
       </c>
       <c r="BC161" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>7</v>
+      </c>
+      <c r="O162" t="n">
+        <v>7</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0.005717658852960364</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
+      <c r="AT162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -29698,7 +29846,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10">
@@ -29708,7 +29856,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
@@ -29760,7 +29908,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16711</v>
+        <v>18138</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d041/2026-2029.xlsx
+++ b/diseases/d041/2026-2029.xlsx
@@ -29730,6 +29730,151 @@
         </is>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>10</v>
+      </c>
+      <c r="O163" t="n">
+        <v>10</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0.008168084075657663</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
+      <c r="AT163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29763,7 +29908,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -29846,7 +29991,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10">
@@ -29856,7 +30001,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -29908,7 +30053,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18138</v>
+        <v>18148</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d041/2026-2029.xlsx
+++ b/diseases/d041/2026-2029.xlsx
@@ -29875,6 +29875,151 @@
         </is>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>7</v>
+      </c>
+      <c r="O164" t="n">
+        <v>7</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0.005717658852960364</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
+      <c r="AT164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29908,7 +30053,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -29991,7 +30136,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -30001,7 +30146,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -30053,7 +30198,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18148</v>
+        <v>18155</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d041/2026-2029.xlsx
+++ b/diseases/d041/2026-2029.xlsx
@@ -25850,12 +25850,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -25889,10 +25889,10 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>149</v>
+        <v>14</v>
       </c>
       <c r="O140" t="n">
-        <v>149</v>
+        <v>14</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
@@ -26001,12 +26001,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -26040,10 +26040,10 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>149</v>
+        <v>14</v>
       </c>
       <c r="O141" t="n">
-        <v>149</v>
+        <v>14</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-FJ:national</t>
         </is>
       </c>
       <c r="AD141" t="inlineStr">
@@ -26198,7 +26198,7 @@
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
@@ -26235,12 +26235,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -26274,10 +26274,10 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>45</v>
+        <v>149</v>
       </c>
       <c r="O142" t="n">
-        <v>45</v>
+        <v>149</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
@@ -26386,12 +26386,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -26425,10 +26425,10 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>45</v>
+        <v>149</v>
       </c>
       <c r="O143" t="n">
-        <v>45</v>
+        <v>149</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr">
@@ -26583,7 +26583,7 @@
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
@@ -26620,12 +26620,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -26659,10 +26659,10 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="O144" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
@@ -26771,12 +26771,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -26810,10 +26810,10 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="O145" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
@@ -26857,7 +26857,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr">
@@ -26968,7 +26968,7 @@
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
@@ -27005,12 +27005,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -27044,10 +27044,10 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O146" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
@@ -27156,12 +27156,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -27195,10 +27195,10 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O147" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr">
@@ -27353,7 +27353,7 @@
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
@@ -27390,12 +27390,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -27429,10 +27429,10 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="O148" t="n">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
@@ -27541,12 +27541,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -27580,10 +27580,10 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="O149" t="n">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr">
@@ -27738,7 +27738,7 @@
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
@@ -27775,12 +27775,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -27814,10 +27814,10 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="O150" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
@@ -27926,12 +27926,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -27965,10 +27965,10 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="O151" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr">
@@ -28123,7 +28123,7 @@
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
@@ -28160,12 +28160,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -28190,7 +28190,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -28199,81 +28199,87 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O152" t="n">
-        <v>4</v>
-      </c>
-      <c r="R152" t="n">
-        <v>0.003267233630263065</v>
+        <v>2</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS; SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
       <c r="AT152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -28300,17 +28306,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -28335,7 +28341,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -28344,81 +28350,170 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O153" t="n">
-        <v>12</v>
-      </c>
-      <c r="R153" t="n">
-        <v>0.009801700890789196</v>
-      </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN153" t="b">
+        <v>1</v>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS; SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
       <c r="AT153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -28480,7 +28575,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -28489,13 +28584,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O154" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R154" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -28625,7 +28720,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -28634,13 +28729,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O155" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R155" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.009801700890789196</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -28770,7 +28865,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -28779,13 +28874,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O156" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="R156" t="n">
-        <v>0.00898489248322343</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -28885,12 +28980,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -28915,25 +29010,22 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N157" t="n">
-        <v>1427</v>
+        <v>3</v>
       </c>
       <c r="O157" t="n">
-        <v>1427</v>
-      </c>
-      <c r="Q157" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R157" t="n">
-        <v>0.1009969404095159</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -28966,17 +29058,17 @@
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -28986,22 +29078,22 @@
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29063,22 +29155,22 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N158" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O158" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R158" t="n">
-        <v>0.004084042037828832</v>
+        <v>0.00898489248322343</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -29178,12 +29270,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -29208,7 +29300,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -29217,13 +29309,16 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>1</v>
+        <v>1427</v>
       </c>
       <c r="O159" t="n">
-        <v>1</v>
+        <v>1427</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.1009969404095159</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -29256,17 +29351,17 @@
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -29276,22 +29371,22 @@
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -29323,12 +29418,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -29353,7 +29448,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -29362,81 +29457,87 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="O160" t="n">
-        <v>7</v>
-      </c>
-      <c r="R160" t="n">
-        <v>0.005717658852960364</v>
+        <v>37</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS; SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -29463,17 +29564,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -29498,7 +29599,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -29507,81 +29608,170 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="O161" t="n">
-        <v>7</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0.005717658852960364</v>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>37</v>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>country:CN-CQ:national</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN161" t="b">
+        <v>1</v>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS; SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
       <c r="AT161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -29613,12 +29803,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -29643,7 +29833,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -29652,81 +29842,87 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>7</v>
+        <v>159</v>
       </c>
       <c r="O162" t="n">
-        <v>7</v>
-      </c>
-      <c r="R162" t="n">
-        <v>0.005717658852960364</v>
+        <v>159</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS; SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
       <c r="AT162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -29753,17 +29949,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -29788,90 +29984,179 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N163" t="n">
-        <v>10</v>
+        <v>159</v>
       </c>
       <c r="O163" t="n">
-        <v>10</v>
-      </c>
-      <c r="R163" t="n">
-        <v>0.008168084075657663</v>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>159</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>country:CN-GD:national</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM163" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN163" t="b">
+        <v>1</v>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS; SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
       <c r="AT163" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -29903,118 +30188,2913 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
+          <t>CN-HN</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Hunan, China</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>32</v>
+      </c>
+      <c r="O164" t="n">
+        <v>32</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS; SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="AT164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>CN-HN</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Hunan, China</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>32</v>
+      </c>
+      <c r="O165" t="n">
+        <v>32</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:CN-HN:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS; SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="AT165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>2</v>
+      </c>
+      <c r="O166" t="n">
+        <v>2</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS; SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="AT166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>CN-JS</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Jiangsu, China</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>2</v>
+      </c>
+      <c r="O167" t="n">
+        <v>2</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS; SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="AT167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>CN-LN</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Liaoning, China</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>3</v>
+      </c>
+      <c r="O168" t="n">
+        <v>3</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS; SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="AT168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>CN-LN</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Liaoning, China</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>3</v>
+      </c>
+      <c r="O169" t="n">
+        <v>3</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>country:CN-LN:national</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN169" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS; SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="AT169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+        </is>
+      </c>
+      <c r="BC169" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>CN-SC</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Sichuan, China</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>55</v>
+      </c>
+      <c r="O170" t="n">
+        <v>55</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS; SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="AT170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>CN-SC</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Sichuan, China</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>55</v>
+      </c>
+      <c r="O171" t="n">
+        <v>55</v>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>country:CN-SC:national</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN171" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS; SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="AT171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS; SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="AT172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>CN-SH</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN173" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS; SER_CN_PROV_REPORT_ACUTE_HEMORRHAGIC_CONJUNCTIVITIS</t>
+        </is>
+      </c>
+      <c r="AT173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+        </is>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
+        <is>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
+      <c r="G174" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>D041</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Acute Hemorrhagic Conjunctivitis</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
         <is>
           <t>急性出血性结膜炎</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
+      <c r="K174" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>5</v>
+      </c>
+      <c r="O174" t="n">
+        <v>5</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0.004084042037828832</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr"/>
+      <c r="AT174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV174" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC174" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>1</v>
+      </c>
+      <c r="O175" t="n">
+        <v>1</v>
+      </c>
+      <c r="R175" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr"/>
+      <c r="AT175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV175" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA175" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB175" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC175" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>7</v>
+      </c>
+      <c r="O176" t="n">
+        <v>7</v>
+      </c>
+      <c r="R176" t="n">
+        <v>0.005717658852960364</v>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP176" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr"/>
+      <c r="AT176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV176" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA176" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB176" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC176" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>7</v>
+      </c>
+      <c r="O177" t="n">
+        <v>7</v>
+      </c>
+      <c r="R177" t="n">
+        <v>0.005717658852960364</v>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr"/>
+      <c r="AT177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV177" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA177" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB177" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC177" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>7</v>
+      </c>
+      <c r="O178" t="n">
+        <v>7</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0.005717658852960364</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr"/>
+      <c r="AT178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA178" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB178" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC178" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>10</v>
+      </c>
+      <c r="O179" t="n">
+        <v>10</v>
+      </c>
+      <c r="R179" t="n">
+        <v>0.008168084075657663</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP179" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr"/>
+      <c r="AT179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV179" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA179" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB179" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC179" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="M164" t="inlineStr">
+      <c r="M180" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N164" t="n">
+      <c r="N180" t="n">
         <v>7</v>
       </c>
-      <c r="O164" t="n">
+      <c r="O180" t="n">
         <v>7</v>
       </c>
-      <c r="R164" t="n">
+      <c r="R180" t="n">
         <v>0.005717658852960364</v>
       </c>
-      <c r="S164" t="inlineStr">
+      <c r="S180" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO164" t="inlineStr">
+      <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP164" t="inlineStr">
+      <c r="AP180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR164" t="inlineStr">
+      <c r="AR180" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS164" t="inlineStr"/>
-      <c r="AT164" t="n">
+      <c r="AS180" t="inlineStr"/>
+      <c r="AT180" t="n">
         <v>0</v>
       </c>
-      <c r="AU164" t="inlineStr">
+      <c r="AU180" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV164" t="inlineStr">
+      <c r="AV180" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW164" t="inlineStr">
+      <c r="AW180" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX164" t="inlineStr">
+      <c r="AX180" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY164" t="inlineStr">
+      <c r="AY180" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ164" t="inlineStr">
+      <c r="AZ180" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA164" t="inlineStr">
+      <c r="BA180" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB164" t="inlineStr">
+      <c r="BB180" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC164" t="inlineStr">
+      <c r="BC180" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -30136,7 +33216,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10">
@@ -30146,7 +33226,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -30166,7 +33246,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -30198,7 +33278,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18155</v>
+        <v>18457</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d041/2026-2029.xlsx
+++ b/diseases/d041/2026-2029.xlsx
@@ -33100,6 +33100,151 @@
         </is>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v>4</v>
+      </c>
+      <c r="O181" t="n">
+        <v>4</v>
+      </c>
+      <c r="R181" t="n">
+        <v>0.003267233630263065</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP181" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr"/>
+      <c r="AT181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU181" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV181" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA181" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB181" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC181" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33133,7 +33278,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -33216,7 +33361,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10">
@@ -33226,7 +33371,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -33278,7 +33423,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18457</v>
+        <v>18461</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d041/2026-2029.xlsx
+++ b/diseases/d041/2026-2029.xlsx
@@ -33245,6 +33245,151 @@
         </is>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>1</v>
+      </c>
+      <c r="O182" t="n">
+        <v>1</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP182" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr"/>
+      <c r="AT182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU182" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV182" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA182" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB182" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC182" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33278,7 +33423,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -33361,7 +33506,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
@@ -33371,7 +33516,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -33423,7 +33568,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18461</v>
+        <v>18462</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d041/2026-2029.xlsx
+++ b/diseases/d041/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4981,6 +4986,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9186,6 +9196,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13006,6 +13021,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16826,6 +16846,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21179,6 +21204,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24987,6 +25017,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29323,6 +29358,11 @@
       <c r="S159" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">

--- a/diseases/d041/2026-2029.xlsx
+++ b/diseases/d041/2026-2029.xlsx
@@ -33430,6 +33430,151 @@
         </is>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N183" t="n">
+        <v>4</v>
+      </c>
+      <c r="O183" t="n">
+        <v>4</v>
+      </c>
+      <c r="R183" t="n">
+        <v>0.003267233630263065</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP183" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr"/>
+      <c r="AT183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU183" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV183" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA183" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB183" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC183" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33463,7 +33608,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -33546,7 +33691,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10">
@@ -33556,7 +33701,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -33608,7 +33753,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18462</v>
+        <v>18466</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d041/2026-2029.xlsx
+++ b/diseases/d041/2026-2029.xlsx
@@ -44640,6 +44640,150 @@
         </is>
       </c>
     </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>acute-hemorrhagic-conjunctivitis</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>JP-11</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Saitama, Japan</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>D041</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>Acute Hemorrhagic Conjunctivitis</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>急性出血性结膜炎</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N308" t="n">
+        <v>1</v>
+      </c>
+      <c r="O308" t="n">
+        <v>1</v>
+      </c>
+      <c r="P308" t="n">
+        <v>1</v>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>HOLD_JP_14be33b983cae6b2ccb33571f1d7</t>
+        </is>
+      </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO308" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP308" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS308" t="inlineStr">
+        <is>
+          <t>HOLD_JP_14be33b983cae6b2ccb33571f1d7</t>
+        </is>
+      </c>
+      <c r="AT308" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV308" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW308" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX308" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY308" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA308" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB308" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC308" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -44673,7 +44817,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -44756,7 +44900,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -44766,7 +44910,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -44818,7 +44962,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19089</v>
+        <v>19090</v>
       </c>
     </row>
     <row r="16">
